--- a/Result/profitability/4923.xlsx
+++ b/Result/profitability/4923.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.925</v>
+        <v>-0.7137500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>21.00625</v>
+        <v>21.9175</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-3.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.17125</v>
+        <v>-1.0425</v>
       </c>
       <c r="N3" t="n">
-        <v>18.37</v>
+        <v>19.025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.4</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0425</v>
+        <v>-0.76125</v>
       </c>
       <c r="N4" t="n">
-        <v>17.45125</v>
+        <v>18.36875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.4424999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>16.885</v>
+        <v>17.46</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.385</v>
+        <v>-0.2325</v>
       </c>
       <c r="N6" t="n">
-        <v>16.37</v>
+        <v>17.35</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.54</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.215</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>16.12625</v>
+        <v>16.44</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -6651,6 +6651,133 @@
       </c>
       <c r="AM49" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>265</v>
+      </c>
+      <c r="D50" t="n">
+        <v>191</v>
+      </c>
+      <c r="E50" t="n">
+        <v>75</v>
+      </c>
+      <c r="F50" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="G50" t="n">
+        <v>14</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>13</v>
+      </c>
+      <c r="K50" t="n">
+        <v>13</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>-0.83625</v>
+      </c>
+      <c r="N50" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0.4599999999999973</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0.01662450307191898</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>-1.192307692307692</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>4.599999999999998</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.1954951126221844</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
